--- a/worked_examples/00_case_analysis_method/tmpl/xlsx/AIHE-CASE00_case_analysis_template.xlsx
+++ b/worked_examples/00_case_analysis_method/tmpl/xlsx/AIHE-CASE00_case_analysis_template.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="R7c352c9074274014"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Framing" sheetId="2" r:id="Rdfec43efa9154e30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Matrix" sheetId="3" r:id="Rb619d07840234e54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Conditions" sheetId="4" r:id="R98afedce84984013"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Recommendation" sheetId="5" r:id="R00b04620545e4cc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="1" r:id="Rd3334f240c3d4fd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Framing" sheetId="2" r:id="Rabed16a6a2cd4d9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Matrix" sheetId="3" r:id="Re4fcaa651eb94fe5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision Conditions" sheetId="4" r:id="R8d8ad40dbe674031"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Recommendation" sheetId="5" r:id="R8bfc43a8ac7941d4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +17,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -40,8 +40,14 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF303236"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -58,6 +64,16 @@
         <x:fgColor rgb="FFEDE3E6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2230"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F0E7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="18">
     <x:border/>
@@ -170,18 +186,18 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="75">
+  <x:cellXfs count="85">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre"/>
+      <x:alignment/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre"/>
+      <x:alignment/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -189,7 +205,7 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -197,30 +213,30 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -246,34 +262,34 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -314,12 +330,12 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="centre" vertical="centre" wrapText="1"/>
+      <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -345,6 +361,34 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -444,9 +488,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -555,17 +599,17 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="75" t="str">
         <x:v>AIHE-CASE00 — Common Case-Analysis Method</x:v>
       </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
+      <x:c r="B1" s="75"/>
+      <x:c r="C1" s="75"/>
+      <x:c r="D1" s="75"/>
+      <x:c r="E1" s="75"/>
+      <x:c r="F1" s="75"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="16" t="str">
+      <x:c r="A3" s="77" t="str">
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B3" s="28" t="str">
@@ -573,7 +617,7 @@
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="18" t="str">
+      <x:c r="A4" s="79" t="str">
         <x:v>Scope</x:v>
       </x:c>
       <x:c r="B4" s="29" t="str">
@@ -581,7 +625,7 @@
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="18" t="str">
+      <x:c r="A5" s="79" t="str">
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B5" s="29" t="str">
@@ -589,7 +633,7 @@
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="18" t="str">
+      <x:c r="A6" s="79" t="str">
         <x:v>Use</x:v>
       </x:c>
       <x:c r="B6" s="29" t="str">
@@ -597,7 +641,7 @@
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="18" t="str">
+      <x:c r="A7" s="79" t="str">
         <x:v>Recommended sequence</x:v>
       </x:c>
       <x:c r="B7" s="29" t="str">
@@ -605,7 +649,7 @@
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="18" t="str">
+      <x:c r="A8" s="79" t="str">
         <x:v>Documentation</x:v>
       </x:c>
       <x:c r="B8" s="29" t="str">
@@ -613,7 +657,7 @@
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="18" t="str">
+      <x:c r="A9" s="79" t="str">
         <x:v>Data protection</x:v>
       </x:c>
       <x:c r="B9" s="29" t="str">
@@ -621,7 +665,7 @@
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="20" t="str">
+      <x:c r="A10" s="81" t="str">
         <x:v>Status</x:v>
       </x:c>
       <x:c r="B10" s="30" t="str">
@@ -645,10 +689,10 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="42" t="str">
+      <x:c r="A1" s="82" t="str">
         <x:v>Field</x:v>
       </x:c>
-      <x:c r="B1" s="43" t="str">
+      <x:c r="B1" s="83" t="str">
         <x:v>Guidance and response</x:v>
       </x:c>
     </x:row>
@@ -703,7 +747,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a9ceb335a544a19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6cb00124d644193"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -721,22 +765,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="42" t="str">
+      <x:c r="A1" s="82" t="str">
         <x:v>Domain</x:v>
       </x:c>
-      <x:c r="B1" s="62" t="str">
+      <x:c r="B1" s="84" t="str">
         <x:v>Question</x:v>
       </x:c>
-      <x:c r="C1" s="62" t="str">
+      <x:c r="C1" s="84" t="str">
         <x:v>Evidence or response</x:v>
       </x:c>
-      <x:c r="D1" s="62" t="str">
+      <x:c r="D1" s="84" t="str">
         <x:v>Confidence</x:v>
       </x:c>
-      <x:c r="E1" s="62" t="str">
+      <x:c r="E1" s="84" t="str">
         <x:v>Owner</x:v>
       </x:c>
-      <x:c r="F1" s="43" t="str">
+      <x:c r="F1" s="83" t="str">
         <x:v>Action</x:v>
       </x:c>
     </x:row>
@@ -820,7 +864,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5eccfa86a60749c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57de2bffe5424323"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -838,22 +882,22 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="42" t="str">
+      <x:c r="A1" s="82" t="str">
         <x:v>Condition or safeguard</x:v>
       </x:c>
-      <x:c r="B1" s="62" t="str">
+      <x:c r="B1" s="84" t="str">
         <x:v>Rationale</x:v>
       </x:c>
-      <x:c r="C1" s="62" t="str">
+      <x:c r="C1" s="84" t="str">
         <x:v>Owner</x:v>
       </x:c>
-      <x:c r="D1" s="62" t="str">
+      <x:c r="D1" s="84" t="str">
         <x:v>Due date</x:v>
       </x:c>
-      <x:c r="E1" s="62" t="str">
+      <x:c r="E1" s="84" t="str">
         <x:v>Evidence of completion</x:v>
       </x:c>
-      <x:c r="F1" s="43" t="str">
+      <x:c r="F1" s="83" t="str">
         <x:v>Trigger if unmet</x:v>
       </x:c>
     </x:row>
@@ -900,7 +944,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea1cf35b1ebe4b58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45aaab837d8c41df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -914,10 +958,10 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="42" t="str">
+      <x:c r="A1" s="82" t="str">
         <x:v>Element</x:v>
       </x:c>
-      <x:c r="B1" s="43" t="str">
+      <x:c r="B1" s="83" t="str">
         <x:v>Response</x:v>
       </x:c>
     </x:row>
@@ -972,7 +1016,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3096fef0c8b402e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8da387d43b52400b"/>
   </x:tableParts>
 </x:worksheet>
 </file>